--- a/nriss-patch-1/ig/CodeSystem-cs-ruim-property-codes.xlsx
+++ b/nriss-patch-1/ig/CodeSystem-cs-ruim-property-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T13:12:34+00:00</t>
+    <t>2026-03-27T13:20:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-1/ig/CodeSystem-cs-ruim-property-codes.xlsx
+++ b/nriss-patch-1/ig/CodeSystem-cs-ruim-property-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T13:20:16+00:00</t>
+    <t>2026-03-30T07:06:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-1/ig/CodeSystem-cs-ruim-property-codes.xlsx
+++ b/nriss-patch-1/ig/CodeSystem-cs-ruim-property-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:06:10+00:00</t>
+    <t>2026-03-30T07:17:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-1/ig/CodeSystem-cs-ruim-property-codes.xlsx
+++ b/nriss-patch-1/ig/CodeSystem-cs-ruim-property-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:17:30+00:00</t>
+    <t>2026-03-30T07:19:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-1/ig/CodeSystem-cs-ruim-property-codes.xlsx
+++ b/nriss-patch-1/ig/CodeSystem-cs-ruim-property-codes.xlsx
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>CS_RuimPropertyCodes</t>
+    <t>CSRuimPropertyCodes</t>
   </si>
   <si>
     <t>Title</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:19:25+00:00</t>
+    <t>2026-03-30T13:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-1/ig/CodeSystem-cs-ruim-property-codes.xlsx
+++ b/nriss-patch-1/ig/CodeSystem-cs-ruim-property-codes.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T13:31:48+00:00</t>
+    <t>2026-03-30T13:39:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-1/ig/CodeSystem-cs-ruim-property-codes.xlsx
+++ b/nriss-patch-1/ig/CodeSystem-cs-ruim-property-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T13:39:05+00:00</t>
+    <t>2026-03-30T13:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
